--- a/public/downloads/bank-reconciliation-template.xlsx
+++ b/public/downloads/bank-reconciliation-template.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="7">
-        <v>46160.56948193287</v>
+        <v>46160.58105878472</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
